--- a/data/trans_orig/P21D_4_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D_4_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125375</t>
+          <t>125484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>279663</t>
+          <t>279711</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>698</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>205297</t>
+          <t>206046</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230780</t>
+          <t>231615</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235970</t>
+          <t>235969</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>439844</t>
+          <t>440405</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>446655</t>
+          <t>446708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90690</t>
+          <t>90723</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135384</t>
+          <t>135366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142994</t>
+          <t>142977</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>229013</t>
+          <t>229023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237620</t>
+          <t>237427</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,62 +1794,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1684</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1696</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6469</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1684</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>7332</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134729</t>
+          <t>135142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>244864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380605</t>
+          <t>381468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>348</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69461</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68226</t>
+          <t>68189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71017</t>
+          <t>71014</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>139040</t>
+          <t>139120</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>141715</t>
+          <t>141720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -2445,97 +2445,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>124240</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109893</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>309644</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>296939</t>
+          <t>297234</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>305614</t>
+          <t>305665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>609322</t>
+          <t>608259</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>617467</t>
+          <t>617420</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -3131,97 +3131,97 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3183</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4549</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>1319</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4185</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>5438</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>5161</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>550733</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>344130</t>
+          <t>343766</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>897069</t>
+          <t>896792</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24816</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1655083</t>
+          <t>1654336</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1663102</t>
+          <t>1662982</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1571251</t>
+          <t>1570831</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1583779</t>
+          <t>1584206</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3230996</t>
+          <t>3229365</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3245895</t>
+          <t>3245642</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_4_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D_4_R-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>509</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>509</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>126151</t>
+          <t>138200</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125484</t>
+          <t>135903</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>280417</t>
+          <t>292487</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>279711</t>
+          <t>290502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>582</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>210269</t>
+          <t>220737</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206046</t>
+          <t>217401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>234633</t>
+          <t>249601</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>231615</t>
+          <t>246004</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235969</t>
+          <t>250946</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>444902</t>
+          <t>470339</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>440405</t>
+          <t>465246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>446708</t>
+          <t>472282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>236133</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>447406</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>447406</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>447406</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94219</t>
+          <t>92394</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90723</t>
+          <t>90066</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>140202</t>
+          <t>140970</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135366</t>
+          <t>136370</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142977</t>
+          <t>143904</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>234421</t>
+          <t>233364</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>229023</t>
+          <t>228473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237427</t>
+          <t>236690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>139693</t>
+          <t>172729</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135142</t>
+          <t>167822</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>386253</t>
+          <t>374237</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>381468</t>
+          <t>369230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>373</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>70196</t>
+          <t>78127</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68189</t>
+          <t>75973</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71014</t>
+          <t>79013</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>140900</t>
+          <t>162548</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>139120</t>
+          <t>159761</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>141720</t>
+          <t>163433</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>10394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>303278</t>
+          <t>352422</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297234</t>
+          <t>346151</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>305665</t>
+          <t>355469</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>615014</t>
+          <t>705229</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>608259</t>
+          <t>698592</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>617420</t>
+          <t>708257</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3274,27 +3274,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>346996</t>
+          <t>405548</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>343766</t>
+          <t>401860</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3309,27 +3309,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>900911</t>
+          <t>766215</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>896792</t>
+          <t>762391</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>767673</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>767673</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>767673</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>902230</t>
+          <t>767673</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,67 +3504,67 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>21994</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>17667</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>11739</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>26607</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>16447</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>10170</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>26447</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1660397</t>
+          <t>1564889</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1654336</t>
+          <t>1559690</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1662982</t>
+          <t>1567125</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,67 +3617,67 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1578968</t>
+          <t>1680092</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1570831</t>
+          <t>1672380</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1584206</t>
+          <t>1685552</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>3807</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>3244981</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>3236041</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>3250909</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>99,18%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>3807</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>3239365</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>3229365</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>3245642</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
